--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130239901</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130239905</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130239903</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130239891</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130239904</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130239896</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130239902</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130239894</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130239900</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130239895</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130239892</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130239898</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130239899</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>130239893</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130239901</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130239905</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130239903</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130239891</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130239904</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130239896</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130239902</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130239894</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130239900</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130239895</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130239892</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130239898</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130239899</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>130239893</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130239901</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130239905</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130239903</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130239891</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130239904</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130239896</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130239902</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130239894</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130239900</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130239895</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130239892</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130239898</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130239899</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>130239893</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130239901</v>
+        <v>130239905</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500920</v>
+        <v>501260</v>
       </c>
       <c r="R2" t="n">
-        <v>6763442</v>
+        <v>6763657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130239905</v>
+        <v>130239901</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501260</v>
+        <v>500920</v>
       </c>
       <c r="R3" t="n">
-        <v>6763657</v>
+        <v>6763442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130239905</v>
+        <v>130239901</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501260</v>
+        <v>500920</v>
       </c>
       <c r="R2" t="n">
-        <v>6763657</v>
+        <v>6763442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130239901</v>
+        <v>130239905</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500920</v>
+        <v>501260</v>
       </c>
       <c r="R3" t="n">
-        <v>6763442</v>
+        <v>6763657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>130239903</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130239891</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130239904</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130239896</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130239902</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130239894</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130239900</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130239895</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130239892</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130239898</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130239899</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>130239893</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -1641,7 +1641,7 @@
         <v>130239885</v>
       </c>
       <c r="B11" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 58555-2025 artfynd.xlsx
+++ b/artfynd/A 58555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130239901</v>
+        <v>130239885</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500920</v>
+        <v>500908</v>
       </c>
       <c r="R2" t="n">
-        <v>6763442</v>
+        <v>6763436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130239905</v>
+        <v>130239891</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501260</v>
+        <v>500863</v>
       </c>
       <c r="R3" t="n">
-        <v>6763657</v>
+        <v>6763440</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130239903</v>
+        <v>130239892</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501187</v>
+        <v>500856</v>
       </c>
       <c r="R4" t="n">
-        <v>6763622</v>
+        <v>6763439</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130239891</v>
+        <v>130239893</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500863</v>
+        <v>500848</v>
       </c>
       <c r="R5" t="n">
-        <v>6763440</v>
+        <v>6763431</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130239904</v>
+        <v>130239894</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501232</v>
+        <v>500788</v>
       </c>
       <c r="R6" t="n">
-        <v>6763630</v>
+        <v>6763373</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130239896</v>
+        <v>130239895</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500801</v>
+        <v>500788</v>
       </c>
       <c r="R7" t="n">
-        <v>6763354</v>
+        <v>6763365</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130239902</v>
+        <v>130239896</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501120</v>
+        <v>500801</v>
       </c>
       <c r="R8" t="n">
-        <v>6763562</v>
+        <v>6763354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130239894</v>
+        <v>130239897</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500788</v>
+        <v>500823</v>
       </c>
       <c r="R9" t="n">
-        <v>6763373</v>
+        <v>6763361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130239900</v>
+        <v>130239898</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500871</v>
+        <v>500852</v>
       </c>
       <c r="R10" t="n">
-        <v>6763435</v>
+        <v>6763416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130239885</v>
+        <v>130239899</v>
       </c>
       <c r="B11" t="n">
-        <v>92220</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500908</v>
+        <v>500853</v>
       </c>
       <c r="R11" t="n">
-        <v>6763436</v>
+        <v>6763418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130239895</v>
+        <v>130239900</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500788</v>
+        <v>500871</v>
       </c>
       <c r="R12" t="n">
-        <v>6763365</v>
+        <v>6763435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130239892</v>
+        <v>130239901</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500856</v>
+        <v>500920</v>
       </c>
       <c r="R13" t="n">
-        <v>6763439</v>
+        <v>6763442</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130239898</v>
+        <v>130239902</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500852</v>
+        <v>501120</v>
       </c>
       <c r="R14" t="n">
-        <v>6763416</v>
+        <v>6763562</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130239899</v>
+        <v>130239903</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500853</v>
+        <v>501187</v>
       </c>
       <c r="R15" t="n">
-        <v>6763418</v>
+        <v>6763622</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130239893</v>
+        <v>130239904</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500848</v>
+        <v>501232</v>
       </c>
       <c r="R16" t="n">
-        <v>6763431</v>
+        <v>6763630</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,6 +2277,221 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130239905</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tövåsnybodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>501260</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6763657</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130239907</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tövåsnybodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>501244</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6763659</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
